--- a/test-case-exports/Balances.xlsx
+++ b/test-case-exports/Balances.xlsx
@@ -227,7 +227,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-08T15:08:53.193Z</t>
+    <t>2026-09-09T06:44:09.976Z</t>
   </si>
   <si>
     <t>Total test cases</t>
